--- a/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 0,0</t>
+          <t>-14,11; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,78</t>
+          <t>0,0; 17,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 6,04</t>
+          <t>-3,34; 5,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 0,0</t>
+          <t>-18,0; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,31</t>
+          <t>0,0; 42,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,0</t>
+          <t>0,0; 33,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 0,0</t>
+          <t>-27,64; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,95</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 0,0</t>
+          <t>-37,12; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 16,11</t>
+          <t>-10,69; 14,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 0,0</t>
+          <t>-11,85; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,17</t>
+          <t>0,0; 9,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,36</t>
+          <t>-2,98; 1,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,37</t>
+          <t>-1,98; 0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,01</t>
+          <t>-0,62; 3,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-79,73; —</t>
+          <t>-73,36; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 0,0</t>
+          <t>-12,63; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,53</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,79</t>
+          <t>-3,3; 6,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,0; 0,0</t>
+          <t>-13,66; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,85</t>
+          <t>0,0; 37,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,87</t>
+          <t>0,0; 29,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 0,0</t>
+          <t>-28,19; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 0,0</t>
+          <t>-45,2; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 14,99</t>
+          <t>-10,54; 15,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 0,0</t>
+          <t>-12,83; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,89</t>
+          <t>-2,89; 1,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,37</t>
+          <t>-2,3; 0,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,9</t>
+          <t>-0,69; 4,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-73,36; —</t>
+          <t>-76,63; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos laxantes</t>
+          <t>Menores que consumieron medicamentos laxantes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -639,12 +639,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 0,0</t>
+          <t>-13,07; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 18,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 6,06</t>
+          <t>-3,34; 6,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 0,0</t>
+          <t>-17,73; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,37</t>
+          <t>0,0; 42,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,82</t>
+          <t>0,0; 34,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 0,0</t>
+          <t>-28,13; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 0,0</t>
+          <t>-37,09; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 15,4</t>
+          <t>-10,39; 16,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 0,0</t>
+          <t>-11,7; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,93</t>
+          <t>-2,55; 2,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,36</t>
+          <t>-1,97; 0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,05</t>
+          <t>-0,49; 4,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-76,63; —</t>
+          <t>-79,73; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A04-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,22 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.9986571048004232</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.075606464232568</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +626,106 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,07; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 18,78</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>-5.327581317087304</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.843174615894376</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,08</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 6,04</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-17,73; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.0528937650259912</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6504138465672729</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>0.09686337482207034</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,35</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>-1.106076166494676</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.254194045739652</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 42,31</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 34,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>1.831603304358698</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,34 +733,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-9,05</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C10" s="5" t="n">
+        <v>2.124495689420602</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.088470064298685</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -869,204 +758,108 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-28,13; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.195783222876893</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>5.530001963725348</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,93</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-37,09; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C13" s="5" t="n">
+        <v>-1.878465189448133</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6960954901145608</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.286848940050794</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="n">
+        <v>3.880278060623434</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +867,303 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67,49%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>-1.556664752204663</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-10,39; 16,11</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-7.783752962380026</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-11,7; 0,0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,17</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-24,48%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-65,71%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>168,01%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-2,55; 2,36</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 0,37</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 4,01</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-79,73; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.6699937685121946</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="n">
+        <v>1.479603101058779</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>-0.7685149377225911</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>3.236947997753255</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-0.3679903448398719</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.3686572394194704</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="5" t="n">
+        <v>-1.850014591834978</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1.739295103974743</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-0.09134389414463348</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.161052709708982</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.3879613443850362</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-0.302245283716649</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-0.6460821472759614</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>2.109763701416357</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-0.5083705409440511</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.5049855884224264</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.107494023971011</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="n">
+        <v>-0.8703936151553124</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.3490642019578554</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.099980169988971</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.9285651670907691</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1172,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
